--- a/dataset/construct/dataset_splits/data_size/10_percent/tum/fold3.xlsx
+++ b/dataset/construct/dataset_splits/data_size/10_percent/tum/fold3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1664</v>
+        <v>1726</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,119 +625,114 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>77.41136002104091</v>
+        <v>71.1663767840393</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>28.8888888888888</v>
       </c>
       <c r="E2" t="n">
-        <v>31.5334467120181</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="I2" t="n">
+        <v>88</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="K2" t="n">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="L2" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>763</v>
+        <v>7.6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>123</v>
+        <v>6.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>153</v>
+        <v>26.85</v>
       </c>
       <c r="V2" t="n">
-        <v>153</v>
+        <v>0.23</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>27.0562770562771</v>
       </c>
       <c r="X2" t="n">
-        <v>21.7</v>
+        <v>26.5306572035833</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.298039215686275</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>22.2816399286988</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.789128418268</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>114</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>162</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>365</v>
+        <v>592</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -760,119 +740,110 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>86.5307742033615</v>
+        <v>81.5341052551525</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>26.8687356599444</v>
       </c>
       <c r="E3" t="n">
-        <v>30.4878048780487</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>484</v>
+      </c>
+      <c r="I3" t="n">
+        <v>784</v>
+      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>419</v>
       </c>
       <c r="K3" t="n">
-        <v>145</v>
+        <v>1687</v>
       </c>
       <c r="L3" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="M3" t="n">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="N3" t="n">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>28.7</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>28.9661319073084</v>
       </c>
       <c r="X3" t="n">
-        <v>22.25</v>
+        <v>28.2049576036652</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.301526717557252</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.2816399286988</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.4950646217447</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>230</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>582</v>
+        <v>481</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -880,85 +851,85 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>84.6962753821583</v>
+        <v>88.08028322812891</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>23.5078053259871</v>
       </c>
       <c r="E4" t="n">
-        <v>24.5351239669421</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>45</v>
+        <v>726</v>
       </c>
       <c r="I4" t="n">
-        <v>3590</v>
+        <v>396</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>285</v>
       </c>
       <c r="K4" t="n">
-        <v>739</v>
+        <v>1407</v>
       </c>
       <c r="L4" t="n">
-        <v>570</v>
+        <v>104</v>
       </c>
       <c r="M4" t="n">
-        <v>485</v>
+        <v>23</v>
       </c>
       <c r="N4" t="n">
-        <v>1794</v>
+        <v>38</v>
       </c>
       <c r="O4" t="n">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X4" t="n">
-        <v>29.85</v>
+        <v>21.6131702613684</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.313559322033898</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>29.921059332824</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>28.8077434310377</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -979,24 +950,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1429</v>
+        <v>300</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1004,86 +966,88 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>89.07960906406061</v>
+        <v>87.77125827059091</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>24.6913580246913</v>
       </c>
       <c r="E5" t="n">
-        <v>36.71875</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>539</v>
+      </c>
+      <c r="I5" t="n">
+        <v>316</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="K5" t="n">
-        <v>522.4</v>
+        <v>1001</v>
       </c>
       <c r="L5" t="n">
-        <v>255.8</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>169.8</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>948</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>89.5</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>117.8</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>25.55</v>
       </c>
       <c r="V5" t="n">
-        <v>8.800000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>25.8467023172906</v>
       </c>
       <c r="X5" t="n">
-        <v>23.45</v>
+        <v>25.4282983710565</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.138888888888889</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.7458619811561</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.6114412754479</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1092,33 +1056,24 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>122</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1227</v>
+        <v>622</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1126,43 +1081,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>86.8977646905975</v>
+        <v>89.18695401424699</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>23.2525951557093</v>
       </c>
       <c r="E6" t="n">
-        <v>23.3843537414965</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="I6" t="n">
-        <v>1140</v>
+        <v>349</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>302</v>
       </c>
       <c r="K6" t="n">
-        <v>646</v>
+        <v>813</v>
       </c>
       <c r="L6" t="n">
-        <v>212</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="N6" t="n">
-        <v>973</v>
+        <v>18</v>
       </c>
       <c r="O6" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1171,37 +1126,37 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>27.45</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>27.6928953399542</v>
       </c>
       <c r="X6" t="n">
-        <v>23.2</v>
+        <v>26.8406888888731</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.318840579710145</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.9182582123759</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.1655797488585</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1210,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1219,30 +1174,19 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>242</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>959</v>
+        <v>936</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1250,79 +1194,79 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>75.6452314814815</v>
+        <v>91.0289564795802</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>23.1111111111111</v>
       </c>
       <c r="E7" t="n">
-        <v>19.9510204081632</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>396</v>
       </c>
       <c r="I7" t="n">
-        <v>5050</v>
+        <v>148</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="K7" t="n">
-        <v>281</v>
+        <v>851</v>
       </c>
       <c r="L7" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="M7" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N7" t="n">
-        <v>394</v>
+        <v>66</v>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.05</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>20.3717850776674</v>
       </c>
       <c r="X7" t="n">
-        <v>22.4</v>
+        <v>19.8319163664306</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.283524904214559</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>22.6203056614775</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1337,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1349,18 +1293,11 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>178</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
